--- a/Bill of Materials/bodaqs-a8/bodaqs-a8-bom.xlsx
+++ b/Bill of Materials/bodaqs-a8/bodaqs-a8-bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benco\dev\BODAQS\Bill of Materials\bodaqs-a8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA18392-D74E-4E1A-A876-1D890B650F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFD407C-63E9-4BBF-86CD-FB500E4D0EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4875" yWindow="-15915" windowWidth="27345" windowHeight="15105" xr2:uid="{EABFD3E1-8261-462A-B08C-D2CC649C17AC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="93">
   <si>
     <t>Qty</t>
   </si>
@@ -303,6 +303,21 @@
   </si>
   <si>
     <t>Available almost anywhere</t>
+  </si>
+  <si>
+    <t>2.5mm shrink sleeve</t>
+  </si>
+  <si>
+    <t>10mm shrink sleeve(if making y connections)</t>
+  </si>
+  <si>
+    <t>Neutral-cure caulking silicone</t>
+  </si>
+  <si>
+    <t>Available from most hardware shops.</t>
+  </si>
+  <si>
+    <t>Available from most hardware shops and electronics suppliers.</t>
   </si>
 </sst>
 </file>
@@ -717,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{589CF3EB-4223-4C48-8045-4A3E0C0060AB}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" style="4" customWidth="1"/>
@@ -1021,77 +1036,50 @@
         <v>87</v>
       </c>
     </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" t="s">
+        <v>92</v>
+      </c>
+    </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="B23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E27" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1099,109 +1087,136 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>65</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
-        <v>49</v>
+      <c r="A30" s="4">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E30" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
         <v>8</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B34" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E34" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
         <v>6</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B35" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E35" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
         <v>4</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B36" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E36" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B39" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
-        <v>1</v>
-      </c>
-      <c r="B37" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="4">
-        <v>1</v>
-      </c>
-      <c r="B38" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
-        <v>1</v>
-      </c>
-      <c r="B39" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1209,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1217,7 +1232,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1225,7 +1240,7 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1233,15 +1248,15 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1249,35 +1264,59 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B47" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
+        <v>1</v>
+      </c>
+      <c r="B48" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
+        <v>4</v>
+      </c>
+      <c r="B49" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="4">
+        <v>1</v>
+      </c>
+      <c r="B50" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D33" r:id="rId1" xr:uid="{6334B9E2-710A-4DA2-9DD2-E8B6AE267FFA}"/>
-    <hyperlink ref="D28" r:id="rId2" xr:uid="{5CDA5779-27B8-4A99-B2A6-447D944D2A6B}"/>
-    <hyperlink ref="D24" r:id="rId3" xr:uid="{93783C79-3665-4D21-B042-BB8277D76343}"/>
-    <hyperlink ref="D27" r:id="rId4" xr:uid="{152F7622-7DD3-41DE-89EC-E10BB5E5D012}"/>
-    <hyperlink ref="D26" r:id="rId5" xr:uid="{CFF10B3E-B38B-4984-BF39-4A35B2722A7E}"/>
-    <hyperlink ref="D25" r:id="rId6" xr:uid="{C4234C91-11FE-443A-91C4-F64E65B8E5EF}"/>
-    <hyperlink ref="D32" r:id="rId7" xr:uid="{EB9A820D-6EC9-48E6-A6EB-7EE9222F09F0}"/>
-    <hyperlink ref="D31" r:id="rId8" xr:uid="{459B16C0-5E4F-4E98-BBDD-DC46AF98B930}"/>
+    <hyperlink ref="D36" r:id="rId1" xr:uid="{6334B9E2-710A-4DA2-9DD2-E8B6AE267FFA}"/>
+    <hyperlink ref="D31" r:id="rId2" xr:uid="{5CDA5779-27B8-4A99-B2A6-447D944D2A6B}"/>
+    <hyperlink ref="D27" r:id="rId3" xr:uid="{93783C79-3665-4D21-B042-BB8277D76343}"/>
+    <hyperlink ref="D30" r:id="rId4" xr:uid="{152F7622-7DD3-41DE-89EC-E10BB5E5D012}"/>
+    <hyperlink ref="D29" r:id="rId5" xr:uid="{CFF10B3E-B38B-4984-BF39-4A35B2722A7E}"/>
+    <hyperlink ref="D28" r:id="rId6" xr:uid="{C4234C91-11FE-443A-91C4-F64E65B8E5EF}"/>
+    <hyperlink ref="D35" r:id="rId7" xr:uid="{EB9A820D-6EC9-48E6-A6EB-7EE9222F09F0}"/>
+    <hyperlink ref="D34" r:id="rId8" xr:uid="{459B16C0-5E4F-4E98-BBDD-DC46AF98B930}"/>
     <hyperlink ref="D18" r:id="rId9" xr:uid="{B31D275A-3214-4CC7-96EF-08FF33774716}"/>
     <hyperlink ref="D17" r:id="rId10" xr:uid="{04C2E29A-B256-4547-895D-7BF7CA6C6458}"/>
     <hyperlink ref="D16" r:id="rId11" xr:uid="{74A804C1-E8A6-4669-AC8E-003E2AF22B8A}"/>
@@ -1310,14 +1349,14 @@
     <hyperlink ref="C17" r:id="rId38" xr:uid="{001C31E4-CAC5-4E32-A4F1-8D980A7046B4}"/>
     <hyperlink ref="C18" r:id="rId39" xr:uid="{ED1D54F1-34F9-4D59-8280-F7D93DCC5979}"/>
     <hyperlink ref="C19" r:id="rId40" xr:uid="{C86952F4-F06C-47B9-9CEC-1B94025A65A3}"/>
-    <hyperlink ref="C24" r:id="rId41" xr:uid="{BCE7DCFA-B2EC-4B4F-8C7C-18B2E995433C}"/>
-    <hyperlink ref="C25" r:id="rId42" xr:uid="{70A5910C-C3B0-4FBE-BE7E-4FC54F3A923D}"/>
-    <hyperlink ref="C26" r:id="rId43" xr:uid="{76975564-FA97-4024-8557-65CA3D182F3B}"/>
-    <hyperlink ref="C27" r:id="rId44" xr:uid="{1EB9246B-EAFD-4647-9B77-5F3A1C81AC03}"/>
-    <hyperlink ref="C28" r:id="rId45" xr:uid="{5EFEA77F-CE5A-4BFD-BD38-1590533F26CA}"/>
-    <hyperlink ref="C31" r:id="rId46" xr:uid="{5244D5CE-5166-4163-AE13-9D90DF5CD914}"/>
-    <hyperlink ref="C32" r:id="rId47" xr:uid="{58F5CA59-9B6D-42B9-ADEC-47CFBFC31FB5}"/>
-    <hyperlink ref="C33" r:id="rId48" xr:uid="{28497E11-DE40-4B57-9CA3-769AABDB2932}"/>
+    <hyperlink ref="C27" r:id="rId41" xr:uid="{BCE7DCFA-B2EC-4B4F-8C7C-18B2E995433C}"/>
+    <hyperlink ref="C28" r:id="rId42" xr:uid="{70A5910C-C3B0-4FBE-BE7E-4FC54F3A923D}"/>
+    <hyperlink ref="C29" r:id="rId43" xr:uid="{76975564-FA97-4024-8557-65CA3D182F3B}"/>
+    <hyperlink ref="C30" r:id="rId44" xr:uid="{1EB9246B-EAFD-4647-9B77-5F3A1C81AC03}"/>
+    <hyperlink ref="C31" r:id="rId45" xr:uid="{5EFEA77F-CE5A-4BFD-BD38-1590533F26CA}"/>
+    <hyperlink ref="C34" r:id="rId46" xr:uid="{5244D5CE-5166-4163-AE13-9D90DF5CD914}"/>
+    <hyperlink ref="C35" r:id="rId47" xr:uid="{58F5CA59-9B6D-42B9-ADEC-47CFBFC31FB5}"/>
+    <hyperlink ref="C36" r:id="rId48" xr:uid="{28497E11-DE40-4B57-9CA3-769AABDB2932}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Bill of Materials/bodaqs-a8/bodaqs-a8-bom.xlsx
+++ b/Bill of Materials/bodaqs-a8/bodaqs-a8-bom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benco\dev\BODAQS\Bill of Materials\bodaqs-a8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFD407C-63E9-4BBF-86CD-FB500E4D0EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFC637B-777A-40F8-A386-506CC5862F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4875" yWindow="-15915" windowWidth="27345" windowHeight="15105" xr2:uid="{EABFD3E1-8261-462A-B08C-D2CC649C17AC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EABFD3E1-8261-462A-B08C-D2CC649C17AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="93">
   <si>
     <t>Qty</t>
   </si>
@@ -179,9 +179,6 @@
     <t>M3 x 5 x 4.2 heat set brass inserts</t>
   </si>
   <si>
-    <t>M3 x 16 stainless steel socket head capscrews</t>
-  </si>
-  <si>
     <t>M3 x 8 stainless steel socket head capscrews</t>
   </si>
   <si>
@@ -218,15 +215,9 @@
     <t>Multiple vendors - search "M3 brass insert"</t>
   </si>
   <si>
-    <t>M2.5 x 5 stainless steel button head capscrew</t>
-  </si>
-  <si>
     <t>https://www.aliexpress.com/item/32966917947.html</t>
   </si>
   <si>
-    <t>Multiple vendors - search "M2.5 stainless steel buttonhead"</t>
-  </si>
-  <si>
     <t>Link2</t>
   </si>
   <si>
@@ -318,6 +309,15 @@
   </si>
   <si>
     <t>Available from most hardware shops and electronics suppliers.</t>
+  </si>
+  <si>
+    <t>M3 x 12 stainless steel socket head capscrews</t>
+  </si>
+  <si>
+    <t>M2 x 5 stainless steel button head capscrew</t>
+  </si>
+  <si>
+    <t>Multiple vendors - search "M2 stainless steel buttonhead"</t>
   </si>
 </sst>
 </file>
@@ -732,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{589CF3EB-4223-4C48-8045-4A3E0C0060AB}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" style="4" customWidth="1"/>
@@ -753,7 +753,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>3</v>
@@ -767,7 +767,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C3" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>10</v>
@@ -812,7 +812,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>12</v>
@@ -829,46 +829,46 @@
         <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C9" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -876,49 +876,49 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="E10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" t="s">
         <v>68</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C12" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -937,13 +937,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -971,7 +971,7 @@
         <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>27</v>
@@ -988,7 +988,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>27</v>
@@ -1002,16 +1002,16 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1019,10 +1019,10 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1030,39 +1030,39 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" t="s">
         <v>89</v>
-      </c>
-      <c r="E23" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1073,13 +1073,13 @@
         <v>45</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" t="s">
         <v>57</v>
-      </c>
-      <c r="E27" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1087,16 +1087,16 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" t="s">
         <v>54</v>
-      </c>
-      <c r="E28" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1104,16 +1104,16 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" t="s">
         <v>54</v>
-      </c>
-      <c r="E29" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1121,16 +1121,16 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" t="s">
         <v>54</v>
-      </c>
-      <c r="E30" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1138,21 +1138,21 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E31" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1160,63 +1160,54 @@
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" t="s">
         <v>52</v>
-      </c>
-      <c r="E34" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" t="s">
         <v>52</v>
       </c>
-      <c r="E35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
-        <v>4</v>
-      </c>
-      <c r="B36" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E36" t="s">
-        <v>61</v>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
-        <v>32</v>
+      <c r="A38" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>0</v>
+      <c r="A39" s="4">
+        <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1224,7 +1215,7 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1232,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1240,7 +1231,7 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1248,7 +1239,7 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1256,7 +1247,7 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1264,99 +1255,89 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="4">
-        <v>1</v>
-      </c>
-      <c r="B50" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D36" r:id="rId1" xr:uid="{6334B9E2-710A-4DA2-9DD2-E8B6AE267FFA}"/>
-    <hyperlink ref="D31" r:id="rId2" xr:uid="{5CDA5779-27B8-4A99-B2A6-447D944D2A6B}"/>
-    <hyperlink ref="D27" r:id="rId3" xr:uid="{93783C79-3665-4D21-B042-BB8277D76343}"/>
-    <hyperlink ref="D30" r:id="rId4" xr:uid="{152F7622-7DD3-41DE-89EC-E10BB5E5D012}"/>
-    <hyperlink ref="D29" r:id="rId5" xr:uid="{CFF10B3E-B38B-4984-BF39-4A35B2722A7E}"/>
-    <hyperlink ref="D28" r:id="rId6" xr:uid="{C4234C91-11FE-443A-91C4-F64E65B8E5EF}"/>
-    <hyperlink ref="D35" r:id="rId7" xr:uid="{EB9A820D-6EC9-48E6-A6EB-7EE9222F09F0}"/>
-    <hyperlink ref="D34" r:id="rId8" xr:uid="{459B16C0-5E4F-4E98-BBDD-DC46AF98B930}"/>
-    <hyperlink ref="D18" r:id="rId9" xr:uid="{B31D275A-3214-4CC7-96EF-08FF33774716}"/>
-    <hyperlink ref="D17" r:id="rId10" xr:uid="{04C2E29A-B256-4547-895D-7BF7CA6C6458}"/>
-    <hyperlink ref="D16" r:id="rId11" xr:uid="{74A804C1-E8A6-4669-AC8E-003E2AF22B8A}"/>
-    <hyperlink ref="D15" r:id="rId12" xr:uid="{9553A994-012D-4350-8DBE-8DAD1ACAC682}"/>
-    <hyperlink ref="D14" r:id="rId13" xr:uid="{2476B977-9152-4437-9248-4758C1F15EAD}"/>
-    <hyperlink ref="D9" r:id="rId14" xr:uid="{5931422E-D376-45D4-A788-649DACBC1731}"/>
-    <hyperlink ref="D7" r:id="rId15" xr:uid="{FC9199B4-E583-42C1-85F6-BD87E21D7523}"/>
-    <hyperlink ref="D6" r:id="rId16" xr:uid="{7EB66862-E70B-4726-B74A-1112B03C9983}"/>
-    <hyperlink ref="D8" r:id="rId17" xr:uid="{CC56C85C-A155-4A2D-B745-C6584AF8481D}"/>
-    <hyperlink ref="D5" r:id="rId18" xr:uid="{2A2A26EB-CE7D-4404-BC09-2553D7FBB944}"/>
-    <hyperlink ref="D4" r:id="rId19" xr:uid="{3A58358E-4C90-424B-837E-65BDBCFC43B0}"/>
-    <hyperlink ref="D3" r:id="rId20" xr:uid="{61546A31-A9F3-49E6-9568-DC85684C45CE}"/>
-    <hyperlink ref="D2" r:id="rId21" xr:uid="{7C41D2A9-EE1B-40F4-9467-E2B52BF735CD}"/>
-    <hyperlink ref="D19" r:id="rId22" xr:uid="{78949137-9F72-4B24-B89E-C61F421C0582}"/>
-    <hyperlink ref="C2" r:id="rId23" xr:uid="{04A15539-C70F-4C6D-ADC6-2E3F57C3D6A0}"/>
-    <hyperlink ref="C3" r:id="rId24" xr:uid="{AF6BBE17-1208-499A-BDD0-CFF408365E93}"/>
-    <hyperlink ref="C4" r:id="rId25" xr:uid="{7E8EE079-B559-4565-BE8F-F4B01A4F6417}"/>
-    <hyperlink ref="C5" r:id="rId26" xr:uid="{33876105-4F6E-4347-ACFD-DC760A90E77B}"/>
-    <hyperlink ref="C6" r:id="rId27" xr:uid="{120D2EA4-668C-4452-8E67-257A46FBFC84}"/>
-    <hyperlink ref="C7" r:id="rId28" xr:uid="{1E68CA1C-ADA5-445D-A9F0-69B4FE91458F}"/>
-    <hyperlink ref="C8" r:id="rId29" xr:uid="{D8ED49FB-BD53-46D0-8AE4-A4A6A5E228CF}"/>
-    <hyperlink ref="C9" r:id="rId30" xr:uid="{3E5F9B4D-00FB-42AB-B1A7-BBDB449640B9}"/>
-    <hyperlink ref="C10" r:id="rId31" xr:uid="{29262321-595E-4557-B568-810C72B53FF0}"/>
-    <hyperlink ref="C11" r:id="rId32" xr:uid="{3B873A34-DB3D-42F8-8F34-A00473FF958D}"/>
-    <hyperlink ref="C12" r:id="rId33" xr:uid="{43936D75-F104-45E6-847B-11FACB65CDFA}"/>
-    <hyperlink ref="C13" r:id="rId34" xr:uid="{F5947E88-7F76-4EE1-8ECF-E6A49E7D90BC}"/>
-    <hyperlink ref="C14" r:id="rId35" xr:uid="{BF48FF1F-407C-49A3-AB7E-467125423C56}"/>
-    <hyperlink ref="C15" r:id="rId36" xr:uid="{5BB56BAE-7147-49C1-B6B6-013939D67A5C}"/>
-    <hyperlink ref="C16" r:id="rId37" xr:uid="{C84A1395-0DB5-45FE-8D7D-8CF109723416}"/>
-    <hyperlink ref="C17" r:id="rId38" xr:uid="{001C31E4-CAC5-4E32-A4F1-8D980A7046B4}"/>
-    <hyperlink ref="C18" r:id="rId39" xr:uid="{ED1D54F1-34F9-4D59-8280-F7D93DCC5979}"/>
-    <hyperlink ref="C19" r:id="rId40" xr:uid="{C86952F4-F06C-47B9-9CEC-1B94025A65A3}"/>
-    <hyperlink ref="C27" r:id="rId41" xr:uid="{BCE7DCFA-B2EC-4B4F-8C7C-18B2E995433C}"/>
-    <hyperlink ref="C28" r:id="rId42" xr:uid="{70A5910C-C3B0-4FBE-BE7E-4FC54F3A923D}"/>
-    <hyperlink ref="C29" r:id="rId43" xr:uid="{76975564-FA97-4024-8557-65CA3D182F3B}"/>
-    <hyperlink ref="C30" r:id="rId44" xr:uid="{1EB9246B-EAFD-4647-9B77-5F3A1C81AC03}"/>
-    <hyperlink ref="C31" r:id="rId45" xr:uid="{5EFEA77F-CE5A-4BFD-BD38-1590533F26CA}"/>
-    <hyperlink ref="C34" r:id="rId46" xr:uid="{5244D5CE-5166-4163-AE13-9D90DF5CD914}"/>
-    <hyperlink ref="C35" r:id="rId47" xr:uid="{58F5CA59-9B6D-42B9-ADEC-47CFBFC31FB5}"/>
-    <hyperlink ref="C36" r:id="rId48" xr:uid="{28497E11-DE40-4B57-9CA3-769AABDB2932}"/>
+    <hyperlink ref="D31" r:id="rId1" xr:uid="{5CDA5779-27B8-4A99-B2A6-447D944D2A6B}"/>
+    <hyperlink ref="D27" r:id="rId2" xr:uid="{93783C79-3665-4D21-B042-BB8277D76343}"/>
+    <hyperlink ref="D30" r:id="rId3" xr:uid="{152F7622-7DD3-41DE-89EC-E10BB5E5D012}"/>
+    <hyperlink ref="D29" r:id="rId4" xr:uid="{CFF10B3E-B38B-4984-BF39-4A35B2722A7E}"/>
+    <hyperlink ref="D28" r:id="rId5" xr:uid="{C4234C91-11FE-443A-91C4-F64E65B8E5EF}"/>
+    <hyperlink ref="D35" r:id="rId6" xr:uid="{EB9A820D-6EC9-48E6-A6EB-7EE9222F09F0}"/>
+    <hyperlink ref="D34" r:id="rId7" xr:uid="{459B16C0-5E4F-4E98-BBDD-DC46AF98B930}"/>
+    <hyperlink ref="D18" r:id="rId8" xr:uid="{B31D275A-3214-4CC7-96EF-08FF33774716}"/>
+    <hyperlink ref="D17" r:id="rId9" xr:uid="{04C2E29A-B256-4547-895D-7BF7CA6C6458}"/>
+    <hyperlink ref="D16" r:id="rId10" xr:uid="{74A804C1-E8A6-4669-AC8E-003E2AF22B8A}"/>
+    <hyperlink ref="D15" r:id="rId11" xr:uid="{9553A994-012D-4350-8DBE-8DAD1ACAC682}"/>
+    <hyperlink ref="D14" r:id="rId12" xr:uid="{2476B977-9152-4437-9248-4758C1F15EAD}"/>
+    <hyperlink ref="D9" r:id="rId13" xr:uid="{5931422E-D376-45D4-A788-649DACBC1731}"/>
+    <hyperlink ref="D7" r:id="rId14" xr:uid="{FC9199B4-E583-42C1-85F6-BD87E21D7523}"/>
+    <hyperlink ref="D6" r:id="rId15" xr:uid="{7EB66862-E70B-4726-B74A-1112B03C9983}"/>
+    <hyperlink ref="D8" r:id="rId16" xr:uid="{CC56C85C-A155-4A2D-B745-C6584AF8481D}"/>
+    <hyperlink ref="D5" r:id="rId17" xr:uid="{2A2A26EB-CE7D-4404-BC09-2553D7FBB944}"/>
+    <hyperlink ref="D4" r:id="rId18" xr:uid="{3A58358E-4C90-424B-837E-65BDBCFC43B0}"/>
+    <hyperlink ref="D3" r:id="rId19" xr:uid="{61546A31-A9F3-49E6-9568-DC85684C45CE}"/>
+    <hyperlink ref="D2" r:id="rId20" xr:uid="{7C41D2A9-EE1B-40F4-9467-E2B52BF735CD}"/>
+    <hyperlink ref="D19" r:id="rId21" xr:uid="{78949137-9F72-4B24-B89E-C61F421C0582}"/>
+    <hyperlink ref="C2" r:id="rId22" xr:uid="{04A15539-C70F-4C6D-ADC6-2E3F57C3D6A0}"/>
+    <hyperlink ref="C3" r:id="rId23" xr:uid="{AF6BBE17-1208-499A-BDD0-CFF408365E93}"/>
+    <hyperlink ref="C4" r:id="rId24" xr:uid="{7E8EE079-B559-4565-BE8F-F4B01A4F6417}"/>
+    <hyperlink ref="C5" r:id="rId25" xr:uid="{33876105-4F6E-4347-ACFD-DC760A90E77B}"/>
+    <hyperlink ref="C6" r:id="rId26" xr:uid="{120D2EA4-668C-4452-8E67-257A46FBFC84}"/>
+    <hyperlink ref="C7" r:id="rId27" xr:uid="{1E68CA1C-ADA5-445D-A9F0-69B4FE91458F}"/>
+    <hyperlink ref="C8" r:id="rId28" xr:uid="{D8ED49FB-BD53-46D0-8AE4-A4A6A5E228CF}"/>
+    <hyperlink ref="C9" r:id="rId29" xr:uid="{3E5F9B4D-00FB-42AB-B1A7-BBDB449640B9}"/>
+    <hyperlink ref="C10" r:id="rId30" xr:uid="{29262321-595E-4557-B568-810C72B53FF0}"/>
+    <hyperlink ref="C11" r:id="rId31" xr:uid="{3B873A34-DB3D-42F8-8F34-A00473FF958D}"/>
+    <hyperlink ref="C12" r:id="rId32" xr:uid="{43936D75-F104-45E6-847B-11FACB65CDFA}"/>
+    <hyperlink ref="C13" r:id="rId33" xr:uid="{F5947E88-7F76-4EE1-8ECF-E6A49E7D90BC}"/>
+    <hyperlink ref="C14" r:id="rId34" xr:uid="{BF48FF1F-407C-49A3-AB7E-467125423C56}"/>
+    <hyperlink ref="C15" r:id="rId35" xr:uid="{5BB56BAE-7147-49C1-B6B6-013939D67A5C}"/>
+    <hyperlink ref="C16" r:id="rId36" xr:uid="{C84A1395-0DB5-45FE-8D7D-8CF109723416}"/>
+    <hyperlink ref="C17" r:id="rId37" xr:uid="{001C31E4-CAC5-4E32-A4F1-8D980A7046B4}"/>
+    <hyperlink ref="C18" r:id="rId38" xr:uid="{ED1D54F1-34F9-4D59-8280-F7D93DCC5979}"/>
+    <hyperlink ref="C19" r:id="rId39" xr:uid="{C86952F4-F06C-47B9-9CEC-1B94025A65A3}"/>
+    <hyperlink ref="C27" r:id="rId40" xr:uid="{BCE7DCFA-B2EC-4B4F-8C7C-18B2E995433C}"/>
+    <hyperlink ref="C28" r:id="rId41" xr:uid="{70A5910C-C3B0-4FBE-BE7E-4FC54F3A923D}"/>
+    <hyperlink ref="C29" r:id="rId42" xr:uid="{76975564-FA97-4024-8557-65CA3D182F3B}"/>
+    <hyperlink ref="C30" r:id="rId43" xr:uid="{1EB9246B-EAFD-4647-9B77-5F3A1C81AC03}"/>
+    <hyperlink ref="C31" r:id="rId44" xr:uid="{5EFEA77F-CE5A-4BFD-BD38-1590533F26CA}"/>
+    <hyperlink ref="C34" r:id="rId45" xr:uid="{5244D5CE-5166-4163-AE13-9D90DF5CD914}"/>
+    <hyperlink ref="C35" r:id="rId46" xr:uid="{58F5CA59-9B6D-42B9-ADEC-47CFBFC31FB5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
